--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/30_FIELD_ENGINEERING/valcanary_corrective_action_crosswalk.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/30_FIELD_ENGINEERING/valcanary_corrective_action_crosswalk.xlsx
@@ -583,17 +583,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VALEVT-2024-001</t>
+          <t>Event 2024-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -610,17 +610,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VALEVT-2024-001</t>
+          <t>Event 2024-001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VALPART-FLT-009</t>
+          <t>QZ-3009</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VALPO-9000000012</t>
+          <t>PO 9001000012</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -637,17 +637,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALEVT-2024-002</t>
+          <t>Event 2024-002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALPO-9000000004</t>
+          <t>PO 9001000004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VALEVT-2024-003</t>
+          <t>Event 2024-003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VALPART-FAN-006</t>
+          <t>QZ-3006</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VALPO-9000000003</t>
+          <t>PO 9001000003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VALEVT-2024-003</t>
+          <t>Event 2024-003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VALPART-UPSCARD-015</t>
+          <t>QZ-3015</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VALPO-9000000008</t>
+          <t>PO 9001000008</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -718,17 +718,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VALEVT-2024-004</t>
+          <t>Event 2024-004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -745,17 +745,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VALEVT-2024-005</t>
+          <t>Event 2024-005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VALPART-PSU-008</t>
+          <t>QZ-3008</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VALPO-9000000010</t>
+          <t>PO 9001000010</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VALEVT-2024-008</t>
+          <t>Event 2024-008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALPART-BATT-007</t>
+          <t>QZ-3007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VALPO-9000000011</t>
+          <t>PO 9001000011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VALEVT-2024-010</t>
+          <t>Event 2024-010</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VALPART-COUPLER-012</t>
+          <t>QZ-3012</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VALPO-9000000005</t>
+          <t>PO 9001000005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VALEVT-2024-011</t>
+          <t>Event 2024-011</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VALPART-NIC-013</t>
+          <t>QZ-3013</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VALPO-9000000009</t>
+          <t>PO 9001000009</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
